--- a/uploads/class_type.xlsx
+++ b/uploads/class_type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A770B630-E0AE-4142-9C10-2ACC9423773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBA8B22-4E5C-4BFE-853B-0EC94E821669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="142">
   <si>
     <t>subject</t>
   </si>
@@ -85,9 +85,6 @@
     <t xml:space="preserve">MI </t>
   </si>
   <si>
-    <t>CHY</t>
-  </si>
-  <si>
     <t xml:space="preserve">PC </t>
   </si>
   <si>
@@ -256,9 +253,6 @@
     <t>AME</t>
   </si>
   <si>
-    <t>Placement</t>
-  </si>
-  <si>
     <t>NSP</t>
   </si>
   <si>
@@ -412,9 +406,6 @@
     <t>IT W/S/PHY LAB</t>
   </si>
   <si>
-    <t>CP/IT W/S</t>
-  </si>
-  <si>
     <t>PROJ</t>
   </si>
   <si>
@@ -452,6 +443,9 @@
   </si>
   <si>
     <t>OS LAB/DBMS LAB</t>
+  </si>
+  <si>
+    <t>CP LAB/IT W/S</t>
   </si>
 </sst>
 </file>
@@ -837,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B145"/>
+  <dimension ref="A1:B143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.33203125" customWidth="1"/>
@@ -990,7 +984,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -998,7 +992,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
@@ -1013,16 +1007,16 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>24</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -1041,20 +1035,20 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
@@ -1062,7 +1056,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
@@ -1078,7 +1072,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
@@ -1086,7 +1080,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -1094,7 +1088,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -1245,16 +1239,16 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>52</v>
-      </c>
-      <c r="B51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
@@ -1406,7 +1400,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
@@ -1414,7 +1408,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
@@ -1485,8 +1479,8 @@
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>80</v>
+      <c r="A81" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
@@ -1494,15 +1488,15 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>104</v>
+      <c r="A83" t="s">
+        <v>82</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
@@ -1510,7 +1504,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B84" t="s">
         <v>11</v>
@@ -1542,7 +1536,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
         <v>11</v>
@@ -1550,7 +1544,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B89" t="s">
         <v>11</v>
@@ -1638,23 +1632,23 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
@@ -1662,7 +1656,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
@@ -1670,7 +1664,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
@@ -1678,7 +1672,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="B105" t="s">
         <v>12</v>
@@ -1686,7 +1680,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B106" t="s">
         <v>12</v>
@@ -1694,7 +1688,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B107" t="s">
         <v>12</v>
@@ -1702,7 +1696,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B108" t="s">
         <v>12</v>
@@ -1710,7 +1704,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="B109" t="s">
         <v>12</v>
@@ -1718,7 +1712,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B110" t="s">
         <v>12</v>
@@ -1726,7 +1720,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B111" t="s">
         <v>12</v>
@@ -1734,7 +1728,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B112" t="s">
         <v>12</v>
@@ -1742,7 +1736,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B113" t="s">
         <v>12</v>
@@ -1750,7 +1744,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B114" t="s">
         <v>12</v>
@@ -1758,7 +1752,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B115" t="s">
         <v>12</v>
@@ -1766,7 +1760,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B116" t="s">
         <v>12</v>
@@ -1774,7 +1768,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B117" t="s">
         <v>12</v>
@@ -1782,7 +1776,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B118" t="s">
         <v>12</v>
@@ -1790,7 +1784,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B119" t="s">
         <v>12</v>
@@ -1798,15 +1792,15 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B120" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>111</v>
+      <c r="A121" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="B121" t="s">
         <v>12</v>
@@ -1814,15 +1808,15 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B122" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
-        <v>132</v>
+      <c r="A123" t="s">
+        <v>104</v>
       </c>
       <c r="B123" t="s">
         <v>12</v>
@@ -1838,7 +1832,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="B125" t="s">
         <v>12</v>
@@ -1846,7 +1840,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="B126" t="s">
         <v>12</v>
@@ -1854,7 +1848,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="B127" t="s">
         <v>12</v>
@@ -1862,7 +1856,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="B128" t="s">
         <v>12</v>
@@ -1870,7 +1864,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="B129" t="s">
         <v>12</v>
@@ -1878,7 +1872,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B130" t="s">
         <v>12</v>
@@ -1886,7 +1880,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B131" t="s">
         <v>12</v>
@@ -1894,15 +1888,15 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B133" t="s">
         <v>12</v>
@@ -1910,39 +1904,39 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="B134" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>131</v>
+    <row r="135" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A135" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="B135" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+    <row r="136" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
         <v>133</v>
       </c>
       <c r="B136" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A137" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>134</v>
+      </c>
+      <c r="B137" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>135</v>
-      </c>
-      <c r="B137" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A138" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="B138" t="s">
         <v>12</v>
@@ -1950,7 +1944,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B139" t="s">
         <v>12</v>
@@ -1958,7 +1952,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B140" t="s">
         <v>12</v>
@@ -1966,7 +1960,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141" t="s">
         <v>12</v>
@@ -1974,7 +1968,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B142" t="s">
         <v>12</v>
@@ -1982,25 +1976,9 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>142</v>
-      </c>
-      <c r="B144" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>143</v>
-      </c>
-      <c r="B145" t="s">
         <v>12</v>
       </c>
     </row>
